--- a/output/pdf_financials_xlsx/FFOX.xlsx
+++ b/output/pdf_financials_xlsx/FFOX.xlsx
@@ -883,28 +883,28 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.8696739999999999</v>
+        <v>-0.8696739999999999</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2.138734</v>
+        <v>-2.138734</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>2.220492</v>
+        <v>-2.220492</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>5.288157</v>
+        <v>-5.288157</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>3.58168</v>
+        <v>-3.58168</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>3.136897</v>
+        <v>-3.136897</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>2.120378</v>
+        <v>-2.120378</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>5.199844</v>
+        <v>-5.199844</v>
       </c>
     </row>
     <row r="17">
@@ -1039,28 +1039,28 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.8696739999999999</v>
+        <v>-0.8696739999999999</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2.138734</v>
+        <v>-2.138734</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>2.220492</v>
+        <v>-2.220492</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>5.288157</v>
+        <v>-5.288157</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>3.58168</v>
+        <v>-3.58168</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>3.136897</v>
+        <v>-3.136897</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>2.120378</v>
+        <v>-2.120378</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>5.199844</v>
+        <v>-5.199844</v>
       </c>
     </row>
     <row r="21">
@@ -1132,28 +1132,28 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.8696739999999999</v>
+        <v>-0.8696739999999999</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2.138734</v>
+        <v>-2.138734</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>2.220492</v>
+        <v>-2.220492</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>5.288157</v>
+        <v>-5.288157</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>3.58168</v>
+        <v>-3.58168</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>3.136897</v>
+        <v>-3.136897</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>2.120378</v>
+        <v>-2.120378</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>5.199844</v>
+        <v>-5.199844</v>
       </c>
     </row>
     <row r="24">
@@ -1225,28 +1225,28 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>14.494567</v>
+        <v>-14.494567</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>21.38734</v>
+        <v>-21.38734</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>37.0082</v>
+        <v>-37.0082</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-88.13594999999999</v>
+        <v>88.13594999999999</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-119.389333</v>
+        <v>119.389333</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>-104.563233</v>
+        <v>104.563233</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>-21.20378</v>
+        <v>21.20378</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>-27.3676</v>
+        <v>27.3676</v>
       </c>
     </row>
     <row r="27">
@@ -1256,28 +1256,28 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.8696739999999999</v>
+        <v>-0.8696739999999999</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>2.138734</v>
+        <v>-2.138734</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>2.220492</v>
+        <v>-2.220492</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>5.288157</v>
+        <v>-5.288157</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3.58168</v>
+        <v>-3.58168</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>3.136897</v>
+        <v>-3.136897</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>2.120378</v>
+        <v>-2.120378</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>5.199844</v>
+        <v>-5.199844</v>
       </c>
     </row>
     <row r="28">
@@ -1318,28 +1318,28 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.8696739999999999</v>
+        <v>-0.8696739999999999</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>2.138734</v>
+        <v>-2.138734</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>2.220492</v>
+        <v>-2.220492</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>5.326688</v>
+        <v>-5.249626</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>3.614448</v>
+        <v>-3.548912</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>3.156853</v>
+        <v>-3.116941</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>2.140334</v>
+        <v>-2.100422</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>5.218566</v>
+        <v>-5.181122</v>
       </c>
     </row>
     <row r="30">
@@ -1396,28 +1396,28 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -12262,10 +12262,10 @@
         </is>
       </c>
       <c r="K135" s="5" t="n">
-        <v>2.120378</v>
+        <v>-2.120378</v>
       </c>
       <c r="L135" s="5" t="n">
-        <v>5.199844</v>
+        <v>-5.199844</v>
       </c>
     </row>
     <row r="136">
@@ -13090,13 +13090,13 @@
         </is>
       </c>
       <c r="I151" s="5" t="n">
-        <v>3.58168</v>
+        <v>-3.58168</v>
       </c>
       <c r="J151" s="5" t="n">
-        <v>3.136897</v>
+        <v>-3.136897</v>
       </c>
       <c r="K151" s="5" t="n">
-        <v>2.120378</v>
+        <v>-2.120378</v>
       </c>
       <c r="L151" t="inlineStr">
         <is>
@@ -13753,10 +13753,10 @@
         </is>
       </c>
       <c r="H163" s="5" t="n">
-        <v>5.288157</v>
+        <v>-5.288157</v>
       </c>
       <c r="I163" s="5" t="n">
-        <v>3.58168</v>
+        <v>-3.58168</v>
       </c>
       <c r="J163" t="inlineStr">
         <is>
@@ -14010,13 +14010,13 @@
         </is>
       </c>
       <c r="E168" s="5" t="n">
-        <v>0.8696739999999999</v>
+        <v>-0.8696739999999999</v>
       </c>
       <c r="F168" s="5" t="n">
-        <v>2.138734</v>
+        <v>-2.138734</v>
       </c>
       <c r="G168" s="5" t="n">
-        <v>2.220492</v>
+        <v>-2.220492</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/FFOX.xlsx
+++ b/output/pdf_financials_xlsx/FFOX.xlsx
@@ -1481,28 +1481,28 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.646995</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.912642</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.24002</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.579171</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.713745</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.02809</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.409735</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>4.024913</v>
       </c>
     </row>
     <row r="35">
@@ -1543,28 +1543,28 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.646995</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.912642</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.24002</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.579171</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.713745</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1.02809</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.409735</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>4.024913</v>
       </c>
     </row>
     <row r="37">
@@ -1915,28 +1915,28 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.651074</v>
+        <v>0.004079</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.922024</v>
+        <v>0.009382</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.265177</v>
+        <v>0.025157</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.782459</v>
+        <v>0.203288</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.78554</v>
+        <v>0.071795</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.186816</v>
+        <v>0.158726</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.664015</v>
+        <v>0.25428</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>4.252653</v>
+        <v>0.22774</v>
       </c>
     </row>
     <row r="49">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E35" s="5" t="n">

--- a/output/pdf_financials_xlsx/FFOX.xlsx
+++ b/output/pdf_financials_xlsx/FFOX.xlsx
@@ -3949,19 +3949,19 @@
         <v>0</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.154122</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.019667</v>
       </c>
       <c r="G111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001029</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.067638</v>
       </c>
     </row>
     <row r="112">
@@ -4680,19 +4680,19 @@
         <v>0</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.154122</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.019667</v>
       </c>
       <c r="G134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001029</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.067638</v>
       </c>
     </row>
     <row r="135">
@@ -4713,19 +4713,19 @@
         <v>-1.845968</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-4.007433</v>
+        <v>-4.161555</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-4.040904</v>
+        <v>-4.060571</v>
       </c>
       <c r="G135" s="3" t="n">
         <v>-2.570909</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>-1.979644</v>
+        <v>-1.980673</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-3.106758</v>
+        <v>-3.174396</v>
       </c>
     </row>
   </sheetData>
@@ -7710,7 +7710,11 @@
           <t>Purchase of equipment 6</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -8714,7 +8718,11 @@
           <t>Purchase of equipment 6</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -9226,7 +9234,11 @@
           <t>Purchase of equipment 7</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
